--- a/data/Event_Data_NNA08VB-01.xlsx
+++ b/data/Event_Data_NNA08VB-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>03-08-2569 03:08</t>
+          <t>17-10-2569 06:22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>02-08-2569 19:46</t>
+          <t>03-08-2569 03:08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>29-07-2569 07:17</t>
+          <t>02-08-2569 19:46</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -512,14 +512,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>T/R ไม่ทราบสาเหตุ</t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>11-07-2569 06:39</t>
+          <t>29-07-2569 07:17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07-07-2569 20:20</t>
+          <t>11-07-2569 06:39</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -556,14 +556,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
+          <t>T/R ไม่ทราบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>22-06-2569 14:44</t>
+          <t>07-07-2569 20:20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -578,14 +578,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>T/R ไม่ทราบสาเหตุ</t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>12-06-2569 07:39</t>
+          <t>22-06-2569 14:44</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>13-10-2568 15:15</t>
+          <t>12-06-2569 07:39</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -617,19 +617,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>T/L</t>
+          <t>T/R</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>T/L ไม่พบสาเหตุ ครั้งแรก 15.09 น. ทั้งหมด 16.06 น.</t>
+          <t>T/R ไม่ทราบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>19-09-2568 06:21</t>
+          <t>13-10-2568 15:15</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -639,19 +639,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>T/R</t>
+          <t>T/L</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
+          <t>T/L ไม่พบสาเหตุ ครั้งแรก 15.09 น. ทั้งหมด 16.06 น.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>17-09-2568 15:21</t>
+          <t>19-09-2568 06:21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -661,19 +661,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>T/L</t>
+          <t>T/R</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>T/L ไม่พบสาเหตุ</t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>22-08-2568 16:13</t>
+          <t>17-09-2568 15:21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -683,19 +683,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T/R</t>
+          <t>T/L</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>T/R ไม่ทราบสาเหตุ</t>
+          <t>T/L ไม่พบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>03-08-2568 13:55</t>
+          <t>22-08-2568 16:13</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -717,7 +717,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>03-08-2568 06:20</t>
+          <t>03-08-2568 13:55</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -732,14 +732,14 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ T/R ไม่ทราบสาเหตุ </t>
+          <t>T/R ไม่ทราบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09-07-2568 18:02</t>
+          <t>03-08-2568 06:20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -754,14 +754,14 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>T/R ไม่ทราบสาเหตุ</t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ T/R ไม่ทราบสาเหตุ </t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>22-04-2568 14:30</t>
+          <t>09-07-2568 18:02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -771,19 +771,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>T/L</t>
+          <t>T/R</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>T/L ไม่พบสาเหตุ จ่ายไฟ 15.07</t>
+          <t>T/R ไม่ทราบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>18-04-2568 14:02</t>
+          <t>22-04-2568 14:30</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -793,19 +793,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>T/R</t>
+          <t>T/L</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>T/R ไม่ทราบสาเหตุ</t>
+          <t>T/L ไม่พบสาเหตุ จ่ายไฟ 15.07</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05-12-2567 12:33</t>
+          <t>18-04-2568 14:02</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -827,7 +827,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>19-11-2567 12:55</t>
+          <t>05-12-2567 12:33</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -849,7 +849,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>11-08-2567 05:23</t>
+          <t>19-11-2567 12:55</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -859,19 +859,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>T/L</t>
+          <t>T/R</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>T/L สายเฟส A ก่อน NNA08S-11 185 PIC บ.ฮ่อม อาร์คขาด ห่าง สฟฟ.6 กม.</t>
+          <t>T/R ไม่ทราบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>15-07-2567 08:59</t>
+          <t>11-08-2567 05:23</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -886,27 +886,49 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>T/L แบ็คโฮเกี่ยวสายแรงสูง 50 A ขาดเฟส B ห่าง สฟฟ. 10 กม.</t>
+          <t>T/L สายเฟส A ก่อน NNA08S-11 185 PIC บ.ฮ่อม อาร์คขาด ห่าง สฟฟ.6 กม.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>15-07-2567 08:59</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>NNA08VB-01</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>T/L</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>T/L แบ็คโฮเกี่ยวสายแรงสูง 50 A ขาดเฟส B ห่าง สฟฟ. 10 กม.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>12-05-2567 05:08</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>NNA08VB-01</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>NNA08VB-01</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
         <is>
           <t>T/L</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>T/L ไม่พบสาเหตุ</t>
         </is>
